--- a/sup_tables/sup_table_s16_age_correlation.xlsx
+++ b/sup_tables/sup_table_s16_age_correlation.xlsx
@@ -5031,13 +5031,13 @@
         <v>10</v>
       </c>
       <c r="C218" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D218" t="n">
-        <v>-0.456948354748987</v>
+        <v>-0.441383089146071</v>
       </c>
       <c r="E218" t="n">
-        <v>0.135327765403662</v>
+        <v>0.131073947493323</v>
       </c>
       <c r="F218" t="n">
         <v>0.597990777903319</v>
@@ -5091,13 +5091,13 @@
         <v>8</v>
       </c>
       <c r="C221" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D221" t="n">
-        <v>-0.553788793358776</v>
+        <v>-0.544823038354561</v>
       </c>
       <c r="E221" t="n">
-        <v>0.0771401627305293</v>
+        <v>0.0669910789535266</v>
       </c>
       <c r="F221" t="n">
         <v>0.597990777903319</v>
@@ -12225,42 +12225,42 @@
     </row>
     <row r="578">
       <c r="A578" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="B578" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="C578" t="n">
-        <v>7</v>
+        <v>96</v>
       </c>
       <c r="D578" t="n">
-        <v>-0.0357142857142857</v>
+        <v>-0.0111136016799666</v>
       </c>
       <c r="E578" t="n">
-        <v>0.963492063492064</v>
+        <v>0.914418104450346</v>
       </c>
       <c r="F578" t="n">
-        <v>0.999850254567236</v>
+        <v>0.993932722228636</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="B579" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C579" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D579" t="n">
-        <v>0.0303030303030303</v>
+        <v>-0.0666666666666667</v>
       </c>
       <c r="E579" t="n">
-        <v>0.94570980835199</v>
+        <v>0.880092592592593</v>
       </c>
       <c r="F579" t="n">
-        <v>0.999850254567236</v>
+        <v>0.993932722228636</v>
       </c>
     </row>
     <row r="580">
@@ -12268,7 +12268,7 @@
         <v>25</v>
       </c>
       <c r="B580" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C580" t="n">
         <v>7</v>
@@ -12285,42 +12285,42 @@
     </row>
     <row r="581">
       <c r="A581" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="B581" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="C581" t="n">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="D581" t="n">
-        <v>-0.0448312561332628</v>
+        <v>0.0303030303030303</v>
       </c>
       <c r="E581" t="n">
-        <v>0.714531391852392</v>
+        <v>0.94570980835199</v>
       </c>
       <c r="F581" t="n">
-        <v>1</v>
+        <v>0.999850254567236</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="B582" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="C582" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D582" t="n">
-        <v>-0.5</v>
+        <v>-0.0357142857142857</v>
       </c>
       <c r="E582" t="n">
-        <v>1</v>
+        <v>0.963492063492064</v>
       </c>
       <c r="F582" t="n">
-        <v>1</v>
+        <v>0.999850254567236</v>
       </c>
     </row>
     <row r="583">
@@ -12328,16 +12328,16 @@
         <v>91</v>
       </c>
       <c r="B583" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C583" t="n">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="D583" t="n">
-        <v>-0.0909090909090909</v>
+        <v>-0.0448312561332628</v>
       </c>
       <c r="E583" t="n">
-        <v>0.796592401118967</v>
+        <v>0.714531391852392</v>
       </c>
       <c r="F583" t="n">
         <v>1</v>
@@ -12348,16 +12348,16 @@
         <v>91</v>
       </c>
       <c r="B584" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C584" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D584" t="n">
-        <v>0.0579771035652448</v>
+        <v>-0.5</v>
       </c>
       <c r="E584" t="n">
-        <v>0.913131785162327</v>
+        <v>1</v>
       </c>
       <c r="F584" t="n">
         <v>1</v>
@@ -12368,16 +12368,16 @@
         <v>91</v>
       </c>
       <c r="B585" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="C585" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D585" t="n">
-        <v>-0.105409255338946</v>
+        <v>-0.0909090909090909</v>
       </c>
       <c r="E585" t="n">
-        <v>0.894590744661054</v>
+        <v>0.796592401118967</v>
       </c>
       <c r="F585" t="n">
         <v>1</v>
@@ -12388,16 +12388,16 @@
         <v>91</v>
       </c>
       <c r="B586" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C586" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="D586" t="n">
-        <v>-0.00298038603906285</v>
+        <v>0.0579771035652448</v>
       </c>
       <c r="E586" t="n">
-        <v>0.982770634280258</v>
+        <v>0.913131785162327</v>
       </c>
       <c r="F586" t="n">
         <v>1</v>
@@ -12408,16 +12408,16 @@
         <v>91</v>
       </c>
       <c r="B587" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C587" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D587" t="n">
-        <v>0.5</v>
+        <v>-0.105409255338946</v>
       </c>
       <c r="E587" t="n">
-        <v>1</v>
+        <v>0.894590744661054</v>
       </c>
       <c r="F587" t="n">
         <v>1</v>
@@ -12428,16 +12428,16 @@
         <v>91</v>
       </c>
       <c r="B588" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="C588" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="D588" t="n">
-        <v>-0.5</v>
+        <v>-0.00298038603906285</v>
       </c>
       <c r="E588" t="n">
-        <v>1</v>
+        <v>0.982770634280258</v>
       </c>
       <c r="F588" t="n">
         <v>1</v>
@@ -12448,16 +12448,16 @@
         <v>91</v>
       </c>
       <c r="B589" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C589" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D589" t="n">
-        <v>-0.0909090909090909</v>
+        <v>0.5</v>
       </c>
       <c r="E589" t="n">
-        <v>0.796592401118967</v>
+        <v>1</v>
       </c>
       <c r="F589" t="n">
         <v>1</v>
@@ -12468,16 +12468,16 @@
         <v>91</v>
       </c>
       <c r="B590" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C590" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D590" t="n">
-        <v>0.0579771035652448</v>
+        <v>-0.5</v>
       </c>
       <c r="E590" t="n">
-        <v>0.913131785162327</v>
+        <v>1</v>
       </c>
       <c r="F590" t="n">
         <v>1</v>
@@ -12488,16 +12488,16 @@
         <v>91</v>
       </c>
       <c r="B591" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="C591" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D591" t="n">
-        <v>-0.105409255338946</v>
+        <v>-0.0909090909090909</v>
       </c>
       <c r="E591" t="n">
-        <v>0.894590744661054</v>
+        <v>0.796592401118967</v>
       </c>
       <c r="F591" t="n">
         <v>1</v>
@@ -12505,19 +12505,19 @@
     </row>
     <row r="592">
       <c r="A592" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B592" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C592" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D592" t="n">
-        <v>0.2</v>
+        <v>0.0579771035652448</v>
       </c>
       <c r="E592" t="n">
-        <v>0.916666666666667</v>
+        <v>0.913131785162327</v>
       </c>
       <c r="F592" t="n">
         <v>1</v>
@@ -12525,19 +12525,19 @@
     </row>
     <row r="593">
       <c r="A593" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B593" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C593" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D593" t="n">
-        <v>-0.1643852753918</v>
+        <v>-0.105409255338946</v>
       </c>
       <c r="E593" t="n">
-        <v>0.629100305058791</v>
+        <v>0.894590744661054</v>
       </c>
       <c r="F593" t="n">
         <v>1</v>
@@ -12548,16 +12548,16 @@
         <v>93</v>
       </c>
       <c r="B594" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C594" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D594" t="n">
-        <v>0.218679382837538</v>
+        <v>0.2</v>
       </c>
       <c r="E594" t="n">
-        <v>0.518271998214228</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F594" t="n">
         <v>1</v>
@@ -12568,16 +12568,16 @@
         <v>93</v>
       </c>
       <c r="B595" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="C595" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D595" t="n">
-        <v>0.060245336588985</v>
+        <v>-0.1643852753918</v>
       </c>
       <c r="E595" t="n">
-        <v>0.88731302189019</v>
+        <v>0.629100305058791</v>
       </c>
       <c r="F595" t="n">
         <v>1</v>
@@ -12588,16 +12588,16 @@
         <v>93</v>
       </c>
       <c r="B596" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C596" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D596" t="n">
-        <v>0.210818510677892</v>
+        <v>0.218679382837538</v>
       </c>
       <c r="E596" t="n">
-        <v>0.789181489322108</v>
+        <v>0.518271998214228</v>
       </c>
       <c r="F596" t="n">
         <v>1</v>
@@ -12608,16 +12608,16 @@
         <v>93</v>
       </c>
       <c r="B597" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C597" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D597" t="n">
-        <v>0.0556561034984226</v>
+        <v>0.060245336588985</v>
       </c>
       <c r="E597" t="n">
-        <v>0.843822709960375</v>
+        <v>0.88731302189019</v>
       </c>
       <c r="F597" t="n">
         <v>1</v>
@@ -12628,16 +12628,16 @@
         <v>93</v>
       </c>
       <c r="B598" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C598" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D598" t="n">
-        <v>0.106078967061087</v>
+        <v>0.210818510677892</v>
       </c>
       <c r="E598" t="n">
-        <v>0.718154328077731</v>
+        <v>0.789181489322108</v>
       </c>
       <c r="F598" t="n">
         <v>1</v>
@@ -12648,16 +12648,16 @@
         <v>93</v>
       </c>
       <c r="B599" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C599" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D599" t="n">
-        <v>-0.153896752812773</v>
+        <v>0.0556561034984226</v>
       </c>
       <c r="E599" t="n">
-        <v>0.804828816608063</v>
+        <v>0.843822709960375</v>
       </c>
       <c r="F599" t="n">
         <v>1</v>
@@ -12668,16 +12668,16 @@
         <v>93</v>
       </c>
       <c r="B600" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="C600" t="n">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="D600" t="n">
-        <v>0.0410038029705412</v>
+        <v>0.106078967061087</v>
       </c>
       <c r="E600" t="n">
-        <v>0.753705873366822</v>
+        <v>0.718154328077731</v>
       </c>
       <c r="F600" t="n">
         <v>1</v>
@@ -12688,16 +12688,16 @@
         <v>93</v>
       </c>
       <c r="B601" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="C601" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D601" t="n">
-        <v>0.2</v>
+        <v>-0.153896752812773</v>
       </c>
       <c r="E601" t="n">
-        <v>0.916666666666667</v>
+        <v>0.804828816608063</v>
       </c>
       <c r="F601" t="n">
         <v>1</v>
@@ -12708,16 +12708,16 @@
         <v>93</v>
       </c>
       <c r="B602" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C602" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="D602" t="n">
-        <v>-0.5</v>
+        <v>0.0410038029705412</v>
       </c>
       <c r="E602" t="n">
-        <v>1</v>
+        <v>0.753705873366822</v>
       </c>
       <c r="F602" t="n">
         <v>1</v>
@@ -12728,16 +12728,16 @@
         <v>93</v>
       </c>
       <c r="B603" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="C603" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="D603" t="n">
-        <v>-0.0743634539431228</v>
+        <v>0.2</v>
       </c>
       <c r="E603" t="n">
-        <v>0.619350591943587</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F603" t="n">
         <v>1</v>
@@ -12748,16 +12748,16 @@
         <v>93</v>
       </c>
       <c r="B604" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C604" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D604" t="n">
-        <v>0.212511859251621</v>
+        <v>-0.5</v>
       </c>
       <c r="E604" t="n">
-        <v>0.686030866008896</v>
+        <v>1</v>
       </c>
       <c r="F604" t="n">
         <v>1</v>
@@ -12768,16 +12768,16 @@
         <v>93</v>
       </c>
       <c r="B605" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C605" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="D605" t="n">
-        <v>0.5</v>
+        <v>-0.0743634539431228</v>
       </c>
       <c r="E605" t="n">
-        <v>1</v>
+        <v>0.619350591943587</v>
       </c>
       <c r="F605" t="n">
         <v>1</v>
@@ -12788,16 +12788,16 @@
         <v>93</v>
       </c>
       <c r="B606" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C606" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D606" t="n">
-        <v>0.142783716156916</v>
+        <v>0.212511859251621</v>
       </c>
       <c r="E606" t="n">
-        <v>0.571938084601557</v>
+        <v>0.686030866008896</v>
       </c>
       <c r="F606" t="n">
         <v>1</v>
@@ -12808,16 +12808,16 @@
         <v>93</v>
       </c>
       <c r="B607" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="C607" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D607" t="n">
-        <v>-0.0180187492539112</v>
+        <v>0.5</v>
       </c>
       <c r="E607" t="n">
-        <v>0.969415386803199</v>
+        <v>1</v>
       </c>
       <c r="F607" t="n">
         <v>1</v>
@@ -12828,16 +12828,16 @@
         <v>93</v>
       </c>
       <c r="B608" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C608" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D608" t="n">
-        <v>0.5</v>
+        <v>0.142783716156916</v>
       </c>
       <c r="E608" t="n">
-        <v>1</v>
+        <v>0.571938084601557</v>
       </c>
       <c r="F608" t="n">
         <v>1</v>
@@ -12848,16 +12848,16 @@
         <v>93</v>
       </c>
       <c r="B609" t="s">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="C609" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D609" t="n">
-        <v>0.060245336588985</v>
+        <v>-0.0180187492539112</v>
       </c>
       <c r="E609" t="n">
-        <v>0.88731302189019</v>
+        <v>0.969415386803199</v>
       </c>
       <c r="F609" t="n">
         <v>1</v>
@@ -12868,16 +12868,16 @@
         <v>93</v>
       </c>
       <c r="B610" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C610" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D610" t="n">
-        <v>0.210818510677892</v>
+        <v>0.5</v>
       </c>
       <c r="E610" t="n">
-        <v>0.789181489322108</v>
+        <v>1</v>
       </c>
       <c r="F610" t="n">
         <v>1</v>
@@ -12888,16 +12888,16 @@
         <v>93</v>
       </c>
       <c r="B611" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C611" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D611" t="n">
-        <v>0.0556561034984226</v>
+        <v>0.060245336588985</v>
       </c>
       <c r="E611" t="n">
-        <v>0.843822709960375</v>
+        <v>0.88731302189019</v>
       </c>
       <c r="F611" t="n">
         <v>1</v>
@@ -12908,16 +12908,16 @@
         <v>93</v>
       </c>
       <c r="B612" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C612" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D612" t="n">
-        <v>0.106078967061087</v>
+        <v>0.210818510677892</v>
       </c>
       <c r="E612" t="n">
-        <v>0.718154328077731</v>
+        <v>0.789181489322108</v>
       </c>
       <c r="F612" t="n">
         <v>1</v>
@@ -12928,16 +12928,16 @@
         <v>93</v>
       </c>
       <c r="B613" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C613" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D613" t="n">
-        <v>0.4</v>
+        <v>0.0556561034984226</v>
       </c>
       <c r="E613" t="n">
-        <v>0.516666666666667</v>
+        <v>0.843822709960375</v>
       </c>
       <c r="F613" t="n">
         <v>1</v>
@@ -12948,16 +12948,16 @@
         <v>93</v>
       </c>
       <c r="B614" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="C614" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D614" t="n">
-        <v>0.632455532033676</v>
+        <v>0.106078967061087</v>
       </c>
       <c r="E614" t="n">
-        <v>0.367544467966324</v>
+        <v>0.718154328077731</v>
       </c>
       <c r="F614" t="n">
         <v>1</v>
@@ -12968,16 +12968,16 @@
         <v>93</v>
       </c>
       <c r="B615" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C615" t="n">
         <v>5</v>
       </c>
       <c r="D615" t="n">
-        <v>-0.153896752812773</v>
+        <v>0.4</v>
       </c>
       <c r="E615" t="n">
-        <v>0.804828816608063</v>
+        <v>0.516666666666667</v>
       </c>
       <c r="F615" t="n">
         <v>1</v>
@@ -12988,16 +12988,16 @@
         <v>93</v>
       </c>
       <c r="B616" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C616" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="D616" t="n">
-        <v>0.0410038029705412</v>
+        <v>0.632455532033676</v>
       </c>
       <c r="E616" t="n">
-        <v>0.753705873366822</v>
+        <v>0.367544467966324</v>
       </c>
       <c r="F616" t="n">
         <v>1</v>
@@ -13005,19 +13005,19 @@
     </row>
     <row r="617">
       <c r="A617" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="B617" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C617" t="n">
-        <v>97</v>
+        <v>5</v>
       </c>
       <c r="D617" t="n">
-        <v>-0.00924683378029949</v>
+        <v>-0.153896752812773</v>
       </c>
       <c r="E617" t="n">
-        <v>0.928372998473285</v>
+        <v>0.804828816608063</v>
       </c>
       <c r="F617" t="n">
         <v>1</v>
@@ -13025,19 +13025,19 @@
     </row>
     <row r="618">
       <c r="A618" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="B618" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C618" t="n">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="D618" t="n">
-        <v>-0.00104004726680483</v>
+        <v>0.0410038029705412</v>
       </c>
       <c r="E618" t="n">
-        <v>0.992018949622932</v>
+        <v>0.753705873366822</v>
       </c>
       <c r="F618" t="n">
         <v>1</v>
@@ -13048,16 +13048,16 @@
         <v>78</v>
       </c>
       <c r="B619" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C619" t="n">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="D619" t="n">
-        <v>-0.5</v>
+        <v>-0.00104004726680483</v>
       </c>
       <c r="E619" t="n">
-        <v>1</v>
+        <v>0.992018949622932</v>
       </c>
       <c r="F619" t="n">
         <v>1</v>
@@ -13068,16 +13068,16 @@
         <v>78</v>
       </c>
       <c r="B620" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C620" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D620" t="n">
-        <v>-0.0666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="E620" t="n">
-        <v>0.880092592592593</v>
+        <v>1</v>
       </c>
       <c r="F620" t="n">
         <v>1</v>
@@ -16929,7 +16929,7 @@
         <v>36</v>
       </c>
       <c r="C830" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D830"/>
       <c r="E830"/>
@@ -21506,46 +21506,46 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C2" t="n">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="D2" t="n">
         <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>1.19363199056355</v>
+        <v>1.19260621376322</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0000000000000000000000452396431823508</v>
+        <v>0.0000000000000000000000710320475041782</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00000000053274790187564</v>
+        <v>0.000000000222058072251376</v>
       </c>
       <c r="H2" t="n">
         <v>4602</v>
       </c>
       <c r="I2" t="n">
-        <v>1.19751752158275</v>
+        <v>1.19840059699104</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0000000847752305145552</v>
+        <v>0.0000000735539460475986</v>
       </c>
       <c r="K2" t="n">
-        <v>1.29732874926789</v>
+        <v>1.29871476119444</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000000000000127677928319458</v>
+        <v>0.0000000000000984250091701618</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00000000000000000000244294073184694</v>
+        <v>0.00000000000000000000383573056522562</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00000175202143063414</v>
+        <v>0.00000152011488498371</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00000000000395801577790319</v>
+        <v>0.00000000000305117528427502</v>
       </c>
     </row>
     <row r="3">
@@ -21553,46 +21553,46 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C3" t="n">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D3" t="n">
         <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>1.19072839229404</v>
+        <v>1.18932870261127</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000000000000000000011734486267392</v>
+        <v>0.000000000000000000021052430887245</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000000000000372174254777176</v>
+        <v>0.000000000000112341068191988</v>
       </c>
       <c r="H3" t="n">
         <v>4602</v>
       </c>
       <c r="I3" t="n">
-        <v>1.30346701175469</v>
+        <v>1.30446422062844</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00000000000223627528653904</v>
+        <v>0.00000000000185211023396797</v>
       </c>
       <c r="K3" t="n">
-        <v>1.41438314136792</v>
+        <v>1.41606233461594</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00000000000000000138644833132738</v>
+        <v>0.00000000000000000100182313098449</v>
       </c>
       <c r="M3" t="n">
-        <v>0.000000000000000000316831129219583</v>
+        <v>0.000000000000000000568415633955614</v>
       </c>
       <c r="N3" t="n">
         <v>0.0000000000787820025735692</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0000000000000000859597965422978</v>
+        <v>0.0000000000000000621130341210382</v>
       </c>
     </row>
     <row r="4">
@@ -22203,7 +22203,7 @@
         <v>0.0910947782093515</v>
       </c>
       <c r="O16" t="n">
-        <v>0.220606860122654</v>
+        <v>0.227960422126742</v>
       </c>
     </row>
     <row r="17">
@@ -22446,46 +22446,46 @@
         <v>57</v>
       </c>
       <c r="B22" t="n">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C22" t="n">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="D22" t="n">
         <v>19</v>
       </c>
       <c r="E22" t="n">
-        <v>1.04021124764021</v>
+        <v>1.04027955404823</v>
       </c>
       <c r="F22" t="n">
-        <v>0.00592727368265853</v>
+        <v>0.00587393000182298</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0106626165408738</v>
+        <v>0.0108039140203898</v>
       </c>
       <c r="H22" t="n">
         <v>4602</v>
       </c>
       <c r="I22" t="n">
-        <v>1.04923749284498</v>
+        <v>1.048314444836</v>
       </c>
       <c r="J22" t="n">
-        <v>0.109550065875075</v>
+        <v>0.115924582571151</v>
       </c>
       <c r="K22" t="n">
-        <v>1.04451473424607</v>
+        <v>1.04341222089221</v>
       </c>
       <c r="L22" t="n">
-        <v>0.151721335205678</v>
+        <v>0.161581056495447</v>
       </c>
       <c r="M22" t="n">
         <v>0.015020735863493</v>
       </c>
       <c r="N22" t="n">
-        <v>0.212253252632957</v>
+        <v>0.224603878731605</v>
       </c>
       <c r="O22" t="n">
-        <v>0.276668317139767</v>
+        <v>0.294647808903461</v>
       </c>
     </row>
     <row r="23">
@@ -22963,7 +22963,7 @@
         <v>36</v>
       </c>
       <c r="B33" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C33" t="n">
         <v>86</v>
@@ -22984,25 +22984,25 @@
         <v>3918</v>
       </c>
       <c r="I33" t="n">
-        <v>1.20074019520341</v>
+        <v>1.19436369097167</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0538164437670141</v>
+        <v>0.0630447088802177</v>
       </c>
       <c r="K33" t="n">
-        <v>1.17029898803784</v>
+        <v>1.16295237020403</v>
       </c>
       <c r="L33" t="n">
-        <v>0.101921700868868</v>
+        <v>0.119380369590899</v>
       </c>
       <c r="M33" t="n">
         <v>0.079847187054043</v>
       </c>
       <c r="N33" t="n">
-        <v>0.145070413632821</v>
+        <v>0.153478104658501</v>
       </c>
       <c r="O33" t="n">
-        <v>0.210638181795661</v>
+        <v>0.238760739181797</v>
       </c>
     </row>
     <row r="34">
@@ -23799,7 +23799,7 @@
         <v>0.205514927883015</v>
       </c>
       <c r="O50" t="n">
-        <v>0.276668317139767</v>
+        <v>0.276856709129365</v>
       </c>
     </row>
     <row r="51">
@@ -23846,7 +23846,7 @@
         <v>0.205514927883015</v>
       </c>
       <c r="O51" t="n">
-        <v>0.276668317139767</v>
+        <v>0.276856709129365</v>
       </c>
     </row>
     <row r="52">
